--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.13.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,8 +431,8 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.13.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.13.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0013.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0013.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L29: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and â€œp</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and â€œg</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L21: isolated marker/symbol line :: ; 4</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 3."</t>
+          <t>L36: isolated marker/symbol line :: 1.«</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -645,7 +649,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>38</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -654,26 +658,22 @@
       <c r="G3" s="1" t="inlineStr"/>
       <c r="H3" s="1" t="inlineStr"/>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1.â€œ</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: 5.</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: 4."</t>
+          <t>L38: isolated marker/symbol line :: 2.«</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -709,26 +709,22 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 2.â€œ</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 6.</t>
+          <t>L32: isolated marker/symbol line :: 1.“</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 5."</t>
+          <t>L40: isolated marker/symbol line :: 3."</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -755,7 +751,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -764,18 +760,18 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 3.â€œ</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
-      <c r="N5" s="1" t="inlineStr"/>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>L33: isolated marker/symbol line :: 2.“</t>
+        </is>
+      </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L44: isolated marker/symbol line :: 6."</t>
+          <t>L41: isolated marker/symbol line :: 4."</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -811,18 +807,18 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4.â€œ</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
-      <c r="N6" s="1" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>L34: isolated marker/symbol line :: 3.“</t>
+        </is>
+      </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 7."</t>
+          <t>L43: isolated marker/symbol line :: 5."</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -858,18 +854,18 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
-      <c r="N7" s="1" t="inlineStr"/>
+      <c r="N7" s="1" t="inlineStr">
+        <is>
+          <t>L35: isolated marker/symbol line :: 4.“</t>
+        </is>
+      </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L44: isolated marker/symbol line :: 6."</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -905,18 +901,18 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L38: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
-      <c r="N8" s="1" t="inlineStr"/>
+      <c r="N8" s="1" t="inlineStr">
+        <is>
+          <t>L36: isolated marker/symbol line :: 5.</t>
+        </is>
+      </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L46: isolated marker/symbol line :: 7."</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -952,16 +948,20 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
-      <c r="N9" s="1" t="inlineStr"/>
-      <c r="O9" s="1" t="inlineStr"/>
+      <c r="N9" s="1" t="inlineStr">
+        <is>
+          <t>L37: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O9" s="1" t="inlineStr">
+        <is>
+          <t>L48: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
       <c r="R9" s="1" t="inlineStr"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -995,16 +995,20 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
-      <c r="J10" s="1" t="inlineStr">
-        <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ</t>
-        </is>
-      </c>
+      <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
-      <c r="N10" s="1" t="inlineStr"/>
-      <c r="O10" s="1" t="inlineStr"/>
+      <c r="N10" s="1" t="inlineStr">
+        <is>
+          <t>L38: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>L50: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1029,7 +1033,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1038,15 +1042,15 @@
       <c r="G11" s="1" t="inlineStr"/>
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>L42: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7.â€œ</t>
-        </is>
-      </c>
+      <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
-      <c r="N11" s="1" t="inlineStr"/>
+      <c r="N11" s="1" t="inlineStr">
+        <is>
+          <t>L39: isolated marker/symbol line :: 6.</t>
+        </is>
+      </c>
       <c r="O11" s="1" t="inlineStr"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
@@ -1067,12 +1071,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1085,7 +1089,11 @@
       <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
-      <c r="N12" s="1" t="inlineStr"/>
+      <c r="N12" s="1" t="inlineStr">
+        <is>
+          <t>L40: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O12" s="1" t="inlineStr"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr"/>
@@ -1124,7 +1132,11 @@
       <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
-      <c r="N13" s="1" t="inlineStr"/>
+      <c r="N13" s="1" t="inlineStr">
+        <is>
+          <t>L41: isolated marker/symbol line :: “</t>
+        </is>
+      </c>
       <c r="O13" s="1" t="inlineStr"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
@@ -1163,7 +1175,11 @@
       <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
-      <c r="N14" s="1" t="inlineStr"/>
+      <c r="N14" s="1" t="inlineStr">
+        <is>
+          <t>L42: isolated marker/symbol line :: 7.“</t>
+        </is>
+      </c>
       <c r="O14" s="1" t="inlineStr"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
